--- a/Data/Results/Visualizations/INTERCITY/Route_Wise/SilkBoard_to_Madhuravoyal/Average/Master_Results.xlsx
+++ b/Data/Results/Visualizations/INTERCITY/Route_Wise/SilkBoard_to_Madhuravoyal/Average/Master_Results.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF7"/>
+  <dimension ref="A1:BF6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -754,160 +754,160 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>98.16888333333333</v>
+        <v>343.8404</v>
       </c>
       <c r="H2" t="n">
-        <v>85.5448</v>
+        <v>311.5075166666667</v>
       </c>
       <c r="I2" t="n">
-        <v>102.5403079815431</v>
+        <v>305.1665869122799</v>
       </c>
       <c r="J2" t="n">
-        <v>102.5404226319246</v>
+        <v>310.4742418277487</v>
       </c>
       <c r="K2" t="n">
-        <v>76.08025778994646</v>
+        <v>69.11154120244322</v>
       </c>
       <c r="L2" t="n">
-        <v>76.61984720324178</v>
+        <v>63.46076786637193</v>
       </c>
       <c r="M2" t="n">
-        <v>12.62408333333333</v>
+        <v>32.33288333333331</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0001146503815050437</v>
+        <v>-5.307654915468788</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5395894132953174</v>
+        <v>5.650773336071289</v>
       </c>
       <c r="P2" t="n">
-        <v>12.01666666666667</v>
+        <v>31.18333333333333</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>0.3133132329092165</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.3133132329092165</v>
       </c>
       <c r="W2" t="n">
-        <v>10.5</v>
+        <v>23.65</v>
       </c>
       <c r="X2" t="n">
-        <v>5.333333333333333</v>
+        <v>18.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.166666666666667</v>
+        <v>5.549999999999997</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.02708574234946004</v>
+        <v>0.04165231879405064</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1105839661259325</v>
+        <v>0.2136487015115684</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.08349822377647247</v>
+        <v>-0.1719963827175178</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.85</v>
+        <v>25.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="AE2" t="n">
-        <v>6.85</v>
+        <v>25.63333333333333</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.03453093426685515</v>
+        <v>0.155968406398383</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.03453093426685515</v>
+        <v>0.155968406398383</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.466666666666667</v>
+        <v>7.6</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.9166666666666666</v>
+        <v>1.75</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.5500000000000004</v>
+        <v>5.85</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.08000017609170872</v>
+        <v>0.4492738025976991</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.1014311759756502</v>
+        <v>0.3073128194596925</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.02143099988394148</v>
+        <v>0.1419609831380066</v>
       </c>
       <c r="AO2" t="n">
-        <v>15.36666666666667</v>
+        <v>61.42373333333333</v>
       </c>
       <c r="AP2" t="n">
-        <v>10.36666666666667</v>
+        <v>57.69085</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5</v>
+        <v>3.732883333333334</v>
       </c>
       <c r="AR2" t="n">
-        <v>15.89297941842838</v>
+        <v>60.30869650602873</v>
       </c>
       <c r="AS2" t="n">
-        <v>12.28082445094132</v>
+        <v>55.580881691352</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.61215496748706</v>
+        <v>4.727814814676734</v>
       </c>
       <c r="AU2" t="n">
-        <v>9.133333333333333</v>
+        <v>45.18333333333333</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.283333333333333</v>
+        <v>41.38333333333333</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.85</v>
+        <v>3.799999999999997</v>
       </c>
       <c r="AX2" t="n">
-        <v>9.410558976194402</v>
+        <v>44.61908932592698</v>
       </c>
       <c r="AY2" t="n">
-        <v>7.766673171881417</v>
+        <v>38.88632527176938</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.643885804312985</v>
+        <v>5.732764054157599</v>
       </c>
       <c r="BA2" t="n">
-        <v>54.85221666666666</v>
+        <v>150.2833333333333</v>
       </c>
       <c r="BB2" t="n">
-        <v>62.6448</v>
+        <v>192.5166666666667</v>
       </c>
       <c r="BC2" t="n">
-        <v>-7.792583333333333</v>
+        <v>-42.23333333333341</v>
       </c>
       <c r="BD2" t="n">
-        <v>77.09515273421231</v>
+        <v>199.2785933196247</v>
       </c>
       <c r="BE2" t="n">
-        <v>82.2809098670003</v>
+        <v>215.4860733436561</v>
       </c>
       <c r="BF2" t="n">
-        <v>-5.185757132787998</v>
+        <v>-16.20748002403141</v>
       </c>
     </row>
     <row r="3">
@@ -940,170 +940,170 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>25.27086666666667</v>
+        <v>343.8404</v>
       </c>
       <c r="H3" t="n">
-        <v>20.34321666666666</v>
+        <v>299.0182166666667</v>
       </c>
       <c r="I3" t="n">
-        <v>27.18076401749682</v>
+        <v>305.1072776594863</v>
       </c>
       <c r="J3" t="n">
-        <v>27.2938636578444</v>
+        <v>305.2160753980956</v>
       </c>
       <c r="K3" t="n">
-        <v>72.17266749628908</v>
+        <v>69.09808681934425</v>
       </c>
       <c r="L3" t="n">
-        <v>80.50014146258407</v>
+        <v>66.42225595059593</v>
       </c>
       <c r="M3" t="n">
-        <v>4.927650000000011</v>
+        <v>44.82218333333327</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1130996403475812</v>
+        <v>-0.1087977386093257</v>
       </c>
       <c r="O3" t="n">
-        <v>-8.327473966294988</v>
+        <v>2.675830868748321</v>
       </c>
       <c r="P3" t="n">
-        <v>2.683333333333333</v>
+        <v>25.93333333333333</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.3133132329092165</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.3133132329092165</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>23.65</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>16.43333333333333</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>7.216666666666669</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>0.04165231879405064</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>0.08388219724002884</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-0.0422298784459782</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.683333333333333</v>
+        <v>25.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>6.983333333333333</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.683333333333333</v>
+        <v>18.71666666666667</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.01072180369660728</v>
+        <v>0.155968406398383</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>0.03091495950618035</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.01072180369660728</v>
+        <v>0.1250534468922027</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>0.4492738025976991</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>0.2309310830082773</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>0.2183427195894218</v>
       </c>
       <c r="AO3" t="n">
-        <v>6.766666666666667</v>
+        <v>61.42373333333333</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.466666666666667</v>
+        <v>60.01821666666667</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.3</v>
+        <v>1.405516666666664</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.807982530871882</v>
+        <v>60.30149638549678</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.402529837201792</v>
+        <v>57.92889382509147</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.405452693670091</v>
+        <v>2.372602560405312</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.183333333333334</v>
+        <v>45.18333333333333</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.033333333333333</v>
+        <v>42.63333333333333</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.15</v>
+        <v>2.549999999999997</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.29026687551903</v>
+        <v>44.61908932592698</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.965547998422918</v>
+        <v>43.16292539518683</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.3247188770961116</v>
+        <v>1.456163930740146</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.63753333333333</v>
+        <v>150.2833333333333</v>
       </c>
       <c r="BB3" t="n">
-        <v>13.84321666666667</v>
+        <v>167.95</v>
       </c>
       <c r="BC3" t="n">
-        <v>-2.20568333333334</v>
+        <v>-17.66666666666669</v>
       </c>
       <c r="BD3" t="n">
-        <v>16.0717928074093</v>
+        <v>199.2264841873632</v>
       </c>
       <c r="BE3" t="n">
-        <v>18.92578582221969</v>
+        <v>203.7785279380628</v>
       </c>
       <c r="BF3" t="n">
-        <v>-2.853993014810392</v>
+        <v>-4.552043750699596</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PAIR_027</t>
+          <t>PAIR_032</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1122,83 +1122,83 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026_to_29-07-2026\PAIR_027_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026_to_29-07-2026\PAIR_032_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>39.97585</v>
+        <v>356.1224666666666</v>
       </c>
       <c r="H4" t="n">
-        <v>23.74308333333333</v>
+        <v>333.4333333333333</v>
       </c>
       <c r="I4" t="n">
-        <v>14.82892455320712</v>
+        <v>324.8278468558257</v>
       </c>
       <c r="J4" t="n">
-        <v>15.14287648205564</v>
+        <v>330.6538536572841</v>
       </c>
       <c r="K4" t="n">
-        <v>57.87321624947242</v>
+        <v>65.68858194612334</v>
       </c>
       <c r="L4" t="n">
-        <v>38.26683233039817</v>
+        <v>62.88775311063549</v>
       </c>
       <c r="M4" t="n">
-        <v>16.23276666666667</v>
+        <v>22.6891333333333</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3139519288485193</v>
+        <v>-5.826006801458391</v>
       </c>
       <c r="O4" t="n">
-        <v>19.60638391907425</v>
+        <v>2.800828835487849</v>
       </c>
       <c r="P4" t="n">
-        <v>25.86666666666667</v>
+        <v>19.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.1419108710453242</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.1419108710453242</v>
       </c>
       <c r="W4" t="n">
-        <v>25.86666666666667</v>
+        <v>37.61666666666667</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>18.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>25.86666666666667</v>
+        <v>19.51666666666667</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.219860917316257</v>
+        <v>1.601243883509142</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>0.2136487015115684</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.219860917316257</v>
+        <v>1.387595181997574</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1210,86 +1210,86 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-1.166666666666667</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>0.2289474824354939</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>0.3073128194596925</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>-0.07836533702419862</v>
       </c>
       <c r="AO4" t="n">
-        <v>2.616666666666667</v>
+        <v>58.38913333333333</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.02745</v>
+        <v>61.95</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-1.410783333333333</v>
+        <v>-3.560866666666676</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.15122666286036</v>
+        <v>60.39000878394881</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.237008300255083</v>
+        <v>59.1588856042147</v>
       </c>
       <c r="AT4" t="n">
-        <v>-1.085781637394723</v>
+        <v>1.231123179734105</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.816666666666667</v>
+        <v>47.78333333333333</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.183333333333334</v>
+        <v>44.95</v>
       </c>
       <c r="AW4" t="n">
-        <v>-1.366666666666667</v>
+        <v>2.833333333333329</v>
       </c>
       <c r="AX4" t="n">
-        <v>2.457618245090195</v>
+        <v>48.61834668820352</v>
       </c>
       <c r="AY4" t="n">
-        <v>2.895199368072901</v>
+        <v>41.61929530648353</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.437581122982706</v>
+        <v>6.999051381719994</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.675850000000001</v>
+        <v>188.35</v>
       </c>
       <c r="BB4" t="n">
-        <v>15.5323</v>
+        <v>206.6166666666667</v>
       </c>
       <c r="BC4" t="n">
-        <v>-6.856449999999999</v>
+        <v>-18.26666666666671</v>
       </c>
       <c r="BD4" t="n">
-        <v>9.000218727940311</v>
+        <v>213.8473891466835</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.010668813727651</v>
+        <v>229.3547112256146</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.01045008578734041</v>
+        <v>-15.50732207893111</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PAIR_028</t>
+          <t>PAIR_033</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1308,178 +1308,178 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026_to_05-09-2026\PAIR_028_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026_to_05-09-2026\PAIR_033_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>20.26271666666667</v>
+        <v>350.0545666666667</v>
       </c>
       <c r="H5" t="n">
-        <v>19.8356</v>
+        <v>317.3162</v>
       </c>
       <c r="I5" t="n">
-        <v>22.49736924506911</v>
+        <v>320.295003456412</v>
       </c>
       <c r="J5" t="n">
-        <v>22.45363674285612</v>
+        <v>320.9302329433269</v>
       </c>
       <c r="K5" t="n">
-        <v>71.17338391598146</v>
+        <v>66.1266599366777</v>
       </c>
       <c r="L5" t="n">
-        <v>67.91920610273282</v>
+        <v>65.88396841768795</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4271166666666701</v>
+        <v>32.73836666666671</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04373250221298974</v>
+        <v>-0.6352294869149091</v>
       </c>
       <c r="O5" t="n">
-        <v>3.254177813248646</v>
+        <v>0.2426915189897443</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>12.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.383333333333333</v>
+        <v>23.4</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.383333333333333</v>
+        <v>23.4</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1022092770638549</v>
+        <v>0.1419108710453242</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1022092770638549</v>
+        <v>0.1419108710453242</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>37.61666666666667</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>16.43333333333333</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>21.18333333333334</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.601243883509142</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>0.08388219724002884</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.517361686269113</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>8.733333333333333</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>-8.733333333333333</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>0.0468402898266811</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>-0.0468402898266811</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.08333333333333333</v>
+        <v>5.083333333333333</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.08333333333333333</v>
+        <v>-4.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>0.2289474824354939</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.005475177103936694</v>
+        <v>0.2495284473497653</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.005475177103936694</v>
+        <v>-0.02058096491427139</v>
       </c>
       <c r="AO5" t="n">
-        <v>3.639233333333334</v>
+        <v>56.67031666666666</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.933333333333334</v>
+        <v>63.81666666666667</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-1.294099999999999</v>
+        <v>-7.146350000000012</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.966520593106893</v>
+        <v>59.19131521643719</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.72826041501822</v>
+        <v>61.45979625723403</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.7617398219113274</v>
+        <v>-2.268481040796843</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.5</v>
+        <v>46.80091666666667</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.966666666666667</v>
+        <v>46.86666666666667</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.5333333333333332</v>
+        <v>-0.0657499999999942</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.418758869278361</v>
+        <v>47.93000682714188</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.094319836595824</v>
+        <v>46.93257746538925</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.3244390326825366</v>
+        <v>0.99742936175263</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.74015</v>
+        <v>184.9833333333333</v>
       </c>
       <c r="BB5" t="n">
-        <v>11.85226666666667</v>
+        <v>176.3828666666667</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.1121166666666706</v>
+        <v>8.600466666666591</v>
       </c>
       <c r="BD5" t="n">
-        <v>15.00988050562</v>
+        <v>211.201579175843</v>
       </c>
       <c r="BE5" t="n">
-        <v>14.62558131413813</v>
+        <v>212.1576082862871</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.3842991914818707</v>
+        <v>-0.9560291104440921</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PAIR_030</t>
+          <t>PAIR_037</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NONSTRICT</t>
+          <t>STRICT</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1494,350 +1494,164 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\29-07-2026_to_06-09-2026\PAIR_030_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\05-09-2026_to_06-09-2026\PAIR_037_STRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>231.7772166666667</v>
+        <v>261.38705</v>
       </c>
       <c r="H6" t="n">
-        <v>213.89885</v>
+        <v>244.9409666666667</v>
       </c>
       <c r="I6" t="n">
-        <v>231.4242273523428</v>
+        <v>249.1268483717951</v>
       </c>
       <c r="J6" t="n">
-        <v>231.3323956071126</v>
+        <v>249.9072012121763</v>
       </c>
       <c r="K6" t="n">
-        <v>67.59910743007244</v>
+        <v>63.84368844822295</v>
       </c>
       <c r="L6" t="n">
-        <v>70.84744357406082</v>
+        <v>67.45522324597772</v>
       </c>
       <c r="M6" t="n">
-        <v>17.87836666666669</v>
+        <v>16.44608333333329</v>
       </c>
       <c r="N6" t="n">
-        <v>0.09183174523019488</v>
+        <v>-0.7803528403811981</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.248336143988382</v>
+        <v>-3.611534797754771</v>
       </c>
       <c r="P6" t="n">
-        <v>-12.46666666666667</v>
+        <v>-16.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>21.51666666666667</v>
+        <v>20.98333333333333</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>21.51666666666667</v>
+        <v>20.98333333333333</v>
       </c>
       <c r="T6" t="n">
-        <v>0.814768997799896</v>
+        <v>0.3053571304336727</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.814768997799896</v>
+        <v>0.3053571304336727</v>
       </c>
       <c r="W6" t="n">
         <v>3.666666666666667</v>
       </c>
       <c r="X6" t="n">
-        <v>18.1</v>
+        <v>16.43333333333333</v>
       </c>
       <c r="Y6" t="n">
-        <v>-14.43333333333333</v>
+        <v>-12.76666666666666</v>
       </c>
       <c r="Z6" t="n">
         <v>0.1409484311311202</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.2136487015115684</v>
+        <v>0.08388219724002884</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.07270027038044818</v>
+        <v>0.05706623389109138</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.033333333333333</v>
+        <v>3.033333333333333</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.06666666666666667</v>
+        <v>6.316666666666666</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.966666666666667</v>
+        <v>-3.283333333333333</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>0.005421542589709919</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>0.02429801927644335</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>-0.01887647668673343</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.71055</v>
+        <v>7.283333333333333</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.416666666666667</v>
+        <v>5</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.293883333333333</v>
+        <v>2.283333333333333</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.5708869176953876</v>
+        <v>0.9244772773315977</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.2061655756673897</v>
+        <v>0.2309310830082773</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.3647213420279979</v>
+        <v>0.6935461943233203</v>
       </c>
       <c r="AO6" t="n">
-        <v>26.75</v>
+        <v>33.00371666666667</v>
       </c>
       <c r="AP6" t="n">
-        <v>36.55</v>
+        <v>46.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-9.799999999999997</v>
+        <v>-13.79628333333333</v>
       </c>
       <c r="AR6" t="n">
-        <v>25.92939460092482</v>
+        <v>30.51433266428049</v>
       </c>
       <c r="AS6" t="n">
-        <v>38.59680733466195</v>
+        <v>45.48619791337757</v>
       </c>
       <c r="AT6" t="n">
-        <v>-12.66741273373713</v>
+        <v>-14.97186524909708</v>
       </c>
       <c r="AU6" t="n">
-        <v>24.85</v>
+        <v>29.65</v>
       </c>
       <c r="AV6" t="n">
-        <v>25.63333333333333</v>
+        <v>33.41666666666666</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.7833333333333279</v>
+        <v>-3.766666666666659</v>
       </c>
       <c r="AX6" t="n">
-        <v>25.11723460299349</v>
+        <v>28.67599222426386</v>
       </c>
       <c r="AY6" t="n">
-        <v>26.87122394746974</v>
+        <v>34.42847320024024</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-1.753989344476249</v>
+        <v>-5.752480975976379</v>
       </c>
       <c r="BA6" t="n">
-        <v>148.25</v>
+        <v>163.7666666666667</v>
       </c>
       <c r="BB6" t="n">
-        <v>132.1321833333333</v>
+        <v>136.9743</v>
       </c>
       <c r="BC6" t="n">
-        <v>16.1178166666667</v>
+        <v>26.79236666666671</v>
       </c>
       <c r="BD6" t="n">
-        <v>178.8509938017981</v>
+        <v>188.5603191017646</v>
       </c>
       <c r="BE6" t="n">
-        <v>165.4445500478019</v>
+        <v>169.6534187990338</v>
       </c>
       <c r="BF6" t="n">
-        <v>13.4064437539962</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>PAIR_032</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>32</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>STRICT</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>INTERCITY</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SilkBoard to Madhuravoyal</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\05-09-2026_to_06-09-2026\PAIR_032_STRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>251.8893</v>
-      </c>
-      <c r="H7" t="n">
-        <v>234.6249833333333</v>
-      </c>
-      <c r="I7" t="n">
-        <v>240.4425765887812</v>
-      </c>
-      <c r="J7" t="n">
-        <v>240.7230050078111</v>
-      </c>
-      <c r="K7" t="n">
-        <v>64.24069875201077</v>
-      </c>
-      <c r="L7" t="n">
-        <v>68.13871680530009</v>
-      </c>
-      <c r="M7" t="n">
-        <v>17.2643166666667</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-0.2804284190299029</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-3.89801805328932</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-16.05</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>21.51666666666667</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>21.51666666666667</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.814768997799896</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.814768997799896</v>
-      </c>
-      <c r="W7" t="n">
-        <v>3.666666666666667</v>
-      </c>
-      <c r="X7" t="n">
-        <v>16.43333333333333</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-12.76666666666666</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.1409484311311202</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.08388219724002884</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0.05706623389109138</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.033333333333333</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>6.316666666666666</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-3.283333333333333</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0.005421542589709919</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0.02429801927644335</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-0.01887647668673343</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>7.283333333333333</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.283333333333333</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0.9244772773315977</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.2309310830082773</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0.6935461943233203</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>30.68333333333333</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>43.75068333333333</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>-13.06735</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>28.50220385729329</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>43.296144650172</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>-14.79394079287871</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>27.88333333333333</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>31.78333333333333</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>-3.900000000000002</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>26.94936248085756</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>33.18950889523448</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>-6.240146414376923</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>157.8226333333333</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>131.3409666666667</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>26.4816666666666</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>183.105394001778</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>163.8982401628798</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>19.20715383889819</v>
+        <v>18.9069003027308</v>
       </c>
     </row>
   </sheetData>
@@ -1851,7 +1665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1908,22 +1722,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.3133132329092165</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.3133132329092165</v>
       </c>
     </row>
     <row r="3">
@@ -1938,22 +1752,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10.5</v>
+        <v>23.65</v>
       </c>
       <c r="D3" t="n">
-        <v>5.333333333333333</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="n">
-        <v>5.166666666666667</v>
+        <v>5.549999999999997</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02708574234946004</v>
+        <v>0.04165231879405064</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1105839661259325</v>
+        <v>0.2136487015115684</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.08349822377647247</v>
+        <v>-0.1719963827175178</v>
       </c>
     </row>
     <row r="4">
@@ -1968,22 +1782,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6.85</v>
+        <v>25.7</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E4" t="n">
-        <v>6.85</v>
+        <v>25.63333333333333</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03453093426685515</v>
+        <v>0.155968406398383</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03453093426685515</v>
+        <v>0.155968406398383</v>
       </c>
     </row>
     <row r="5">
@@ -1998,22 +1812,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.466666666666667</v>
+        <v>7.6</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9166666666666666</v>
+        <v>1.75</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5500000000000004</v>
+        <v>5.85</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08000017609170872</v>
+        <v>0.4492738025976991</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1014311759756502</v>
+        <v>0.3073128194596925</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.02143099988394148</v>
+        <v>0.1419609831380066</v>
       </c>
     </row>
     <row r="6">
@@ -2028,22 +1842,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15.36666666666667</v>
+        <v>61.42373333333333</v>
       </c>
       <c r="D6" t="n">
-        <v>10.36666666666667</v>
+        <v>57.69085</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>3.732883333333334</v>
       </c>
       <c r="F6" t="n">
-        <v>15.89297941842838</v>
+        <v>60.30869650602873</v>
       </c>
       <c r="G6" t="n">
-        <v>12.28082445094132</v>
+        <v>55.580881691352</v>
       </c>
       <c r="H6" t="n">
-        <v>3.61215496748706</v>
+        <v>4.727814814676734</v>
       </c>
     </row>
     <row r="7">
@@ -2058,22 +1872,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9.133333333333333</v>
+        <v>45.18333333333333</v>
       </c>
       <c r="D7" t="n">
-        <v>6.283333333333333</v>
+        <v>41.38333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>2.85</v>
+        <v>3.799999999999997</v>
       </c>
       <c r="F7" t="n">
-        <v>9.410558976194402</v>
+        <v>44.61908932592698</v>
       </c>
       <c r="G7" t="n">
-        <v>7.766673171881417</v>
+        <v>38.88632527176938</v>
       </c>
       <c r="H7" t="n">
-        <v>1.643885804312985</v>
+        <v>5.732764054157599</v>
       </c>
     </row>
     <row r="8">
@@ -2088,22 +1902,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>54.85221666666666</v>
+        <v>150.2833333333333</v>
       </c>
       <c r="D8" t="n">
-        <v>62.6448</v>
+        <v>192.5166666666667</v>
       </c>
       <c r="E8" t="n">
-        <v>-7.792583333333333</v>
+        <v>-42.23333333333341</v>
       </c>
       <c r="F8" t="n">
-        <v>77.09515273421231</v>
+        <v>199.2785933196247</v>
       </c>
       <c r="G8" t="n">
-        <v>82.2809098670003</v>
+        <v>215.4860733436561</v>
       </c>
       <c r="H8" t="n">
-        <v>-5.185757132787998</v>
+        <v>-16.20748002403141</v>
       </c>
     </row>
     <row r="9">
@@ -2118,22 +1932,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.3133132329092165</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.3133132329092165</v>
       </c>
     </row>
     <row r="10">
@@ -2148,22 +1962,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>23.65</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>16.43333333333333</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>7.216666666666669</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.04165231879405064</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.08388219724002884</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-0.0422298784459782</v>
       </c>
     </row>
     <row r="11">
@@ -2178,22 +1992,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.683333333333333</v>
+        <v>25.7</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>6.983333333333333</v>
       </c>
       <c r="E11" t="n">
-        <v>2.683333333333333</v>
+        <v>18.71666666666667</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01072180369660728</v>
+        <v>0.155968406398383</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.03091495950618035</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01072180369660728</v>
+        <v>0.1250534468922027</v>
       </c>
     </row>
     <row r="12">
@@ -2208,22 +2022,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.4492738025976991</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.2309310830082773</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.2183427195894218</v>
       </c>
     </row>
     <row r="13">
@@ -2238,22 +2052,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6.766666666666667</v>
+        <v>61.42373333333333</v>
       </c>
       <c r="D13" t="n">
-        <v>3.466666666666667</v>
+        <v>60.01821666666667</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3</v>
+        <v>1.405516666666664</v>
       </c>
       <c r="F13" t="n">
-        <v>6.807982530871882</v>
+        <v>60.30149638549678</v>
       </c>
       <c r="G13" t="n">
-        <v>4.402529837201792</v>
+        <v>57.92889382509147</v>
       </c>
       <c r="H13" t="n">
-        <v>2.405452693670091</v>
+        <v>2.372602560405312</v>
       </c>
     </row>
     <row r="14">
@@ -2268,22 +2082,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4.183333333333334</v>
+        <v>45.18333333333333</v>
       </c>
       <c r="D14" t="n">
-        <v>3.033333333333333</v>
+        <v>42.63333333333333</v>
       </c>
       <c r="E14" t="n">
-        <v>1.15</v>
+        <v>2.549999999999997</v>
       </c>
       <c r="F14" t="n">
-        <v>4.29026687551903</v>
+        <v>44.61908932592698</v>
       </c>
       <c r="G14" t="n">
-        <v>3.965547998422918</v>
+        <v>43.16292539518683</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3247188770961116</v>
+        <v>1.456163930740146</v>
       </c>
     </row>
     <row r="15">
@@ -2298,28 +2112,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11.63753333333333</v>
+        <v>150.2833333333333</v>
       </c>
       <c r="D15" t="n">
-        <v>13.84321666666667</v>
+        <v>167.95</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.20568333333334</v>
+        <v>-17.66666666666669</v>
       </c>
       <c r="F15" t="n">
-        <v>16.0717928074093</v>
+        <v>199.2264841873632</v>
       </c>
       <c r="G15" t="n">
-        <v>18.92578582221969</v>
+        <v>203.7785279380628</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.853993014810392</v>
+        <v>-4.552043750699596</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PAIR_027</t>
+          <t>PAIR_032</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2328,28 +2142,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.1419108710453242</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.1419108710453242</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PAIR_027</t>
+          <t>PAIR_032</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2358,28 +2172,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25.86666666666667</v>
+        <v>37.61666666666667</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>18.1</v>
       </c>
       <c r="E17" t="n">
-        <v>25.86666666666667</v>
+        <v>19.51666666666667</v>
       </c>
       <c r="F17" t="n">
-        <v>1.219860917316257</v>
+        <v>1.601243883509142</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.2136487015115684</v>
       </c>
       <c r="H17" t="n">
-        <v>1.219860917316257</v>
+        <v>1.387595181997574</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PAIR_027</t>
+          <t>PAIR_032</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2391,10 +2205,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -2409,7 +2223,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PAIR_027</t>
+          <t>PAIR_032</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2418,28 +2232,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>-1.166666666666667</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.2289474824354939</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.3073128194596925</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-0.07836533702419862</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PAIR_027</t>
+          <t>PAIR_032</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2448,28 +2262,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.616666666666667</v>
+        <v>58.38913333333333</v>
       </c>
       <c r="D20" t="n">
-        <v>4.02745</v>
+        <v>61.95</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.410783333333333</v>
+        <v>-3.560866666666676</v>
       </c>
       <c r="F20" t="n">
-        <v>2.15122666286036</v>
+        <v>60.39000878394881</v>
       </c>
       <c r="G20" t="n">
-        <v>3.237008300255083</v>
+        <v>59.1588856042147</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.085781637394723</v>
+        <v>1.231123179734105</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PAIR_027</t>
+          <t>PAIR_032</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2478,28 +2292,28 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.816666666666667</v>
+        <v>47.78333333333333</v>
       </c>
       <c r="D21" t="n">
-        <v>4.183333333333334</v>
+        <v>44.95</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.366666666666667</v>
+        <v>2.833333333333329</v>
       </c>
       <c r="F21" t="n">
-        <v>2.457618245090195</v>
+        <v>48.61834668820352</v>
       </c>
       <c r="G21" t="n">
-        <v>2.895199368072901</v>
+        <v>41.61929530648353</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.437581122982706</v>
+        <v>6.999051381719994</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PAIR_027</t>
+          <t>PAIR_032</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2508,28 +2322,28 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8.675850000000001</v>
+        <v>188.35</v>
       </c>
       <c r="D22" t="n">
-        <v>15.5323</v>
+        <v>206.6166666666667</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.856449999999999</v>
+        <v>-18.26666666666671</v>
       </c>
       <c r="F22" t="n">
-        <v>9.000218727940311</v>
+        <v>213.8473891466835</v>
       </c>
       <c r="G22" t="n">
-        <v>9.010668813727651</v>
+        <v>229.3547112256146</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.01045008578734041</v>
+        <v>-15.50732207893111</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PAIR_028</t>
+          <t>PAIR_033</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2538,28 +2352,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.383333333333333</v>
+        <v>23.4</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>1.383333333333333</v>
+        <v>23.4</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1022092770638549</v>
+        <v>0.1419108710453242</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1022092770638549</v>
+        <v>0.1419108710453242</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PAIR_028</t>
+          <t>PAIR_033</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2568,28 +2382,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>37.61666666666667</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>16.43333333333333</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>21.18333333333334</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1.601243883509142</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.08388219724002884</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1.517361686269113</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PAIR_028</t>
+          <t>PAIR_033</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2601,25 +2415,25 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>8.733333333333333</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>-8.733333333333333</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.0468402898266811</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>-0.0468402898266811</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PAIR_028</t>
+          <t>PAIR_033</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2628,28 +2442,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08333333333333333</v>
+        <v>5.083333333333333</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.08333333333333333</v>
+        <v>-4.5</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.2289474824354939</v>
       </c>
       <c r="G26" t="n">
-        <v>0.005475177103936694</v>
+        <v>0.2495284473497653</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.005475177103936694</v>
+        <v>-0.02058096491427139</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PAIR_028</t>
+          <t>PAIR_033</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2658,28 +2472,28 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3.639233333333334</v>
+        <v>56.67031666666666</v>
       </c>
       <c r="D27" t="n">
-        <v>4.933333333333334</v>
+        <v>63.81666666666667</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.294099999999999</v>
+        <v>-7.146350000000012</v>
       </c>
       <c r="F27" t="n">
-        <v>3.966520593106893</v>
+        <v>59.19131521643719</v>
       </c>
       <c r="G27" t="n">
-        <v>4.72826041501822</v>
+        <v>61.45979625723403</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.7617398219113274</v>
+        <v>-2.268481040796843</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PAIR_028</t>
+          <t>PAIR_033</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2688,28 +2502,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3.5</v>
+        <v>46.80091666666667</v>
       </c>
       <c r="D28" t="n">
-        <v>2.966666666666667</v>
+        <v>46.86666666666667</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5333333333333332</v>
+        <v>-0.0657499999999942</v>
       </c>
       <c r="F28" t="n">
-        <v>3.418758869278361</v>
+        <v>47.93000682714188</v>
       </c>
       <c r="G28" t="n">
-        <v>3.094319836595824</v>
+        <v>46.93257746538925</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3244390326825366</v>
+        <v>0.99742936175263</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PAIR_028</t>
+          <t>PAIR_033</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2718,28 +2532,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>11.74015</v>
+        <v>184.9833333333333</v>
       </c>
       <c r="D29" t="n">
-        <v>11.85226666666667</v>
+        <v>176.3828666666667</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1121166666666706</v>
+        <v>8.600466666666591</v>
       </c>
       <c r="F29" t="n">
-        <v>15.00988050562</v>
+        <v>211.201579175843</v>
       </c>
       <c r="G29" t="n">
-        <v>14.62558131413813</v>
+        <v>212.1576082862871</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3842991914818707</v>
+        <v>-0.9560291104440921</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PAIR_030</t>
+          <t>PAIR_037</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2748,28 +2562,28 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>21.51666666666667</v>
+        <v>20.98333333333333</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>21.51666666666667</v>
+        <v>20.98333333333333</v>
       </c>
       <c r="F30" t="n">
-        <v>0.814768997799896</v>
+        <v>0.3053571304336727</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.814768997799896</v>
+        <v>0.3053571304336727</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PAIR_030</t>
+          <t>PAIR_037</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2781,25 +2595,25 @@
         <v>3.666666666666667</v>
       </c>
       <c r="D31" t="n">
-        <v>18.1</v>
+        <v>16.43333333333333</v>
       </c>
       <c r="E31" t="n">
-        <v>-14.43333333333333</v>
+        <v>-12.76666666666666</v>
       </c>
       <c r="F31" t="n">
         <v>0.1409484311311202</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2136487015115684</v>
+        <v>0.08388219724002884</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.07270027038044818</v>
+        <v>0.05706623389109138</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PAIR_030</t>
+          <t>PAIR_037</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2808,28 +2622,28 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2.033333333333333</v>
+        <v>3.033333333333333</v>
       </c>
       <c r="D32" t="n">
-        <v>0.06666666666666667</v>
+        <v>6.316666666666666</v>
       </c>
       <c r="E32" t="n">
-        <v>1.966666666666667</v>
+        <v>-3.283333333333333</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.005421542589709919</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.02429801927644335</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>-0.01887647668673343</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PAIR_030</t>
+          <t>PAIR_037</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2838,28 +2652,28 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4.71055</v>
+        <v>7.283333333333333</v>
       </c>
       <c r="D33" t="n">
-        <v>1.416666666666667</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>3.293883333333333</v>
+        <v>2.283333333333333</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5708869176953876</v>
+        <v>0.9244772773315977</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2061655756673897</v>
+        <v>0.2309310830082773</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3647213420279979</v>
+        <v>0.6935461943233203</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PAIR_030</t>
+          <t>PAIR_037</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2868,28 +2682,28 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>26.75</v>
+        <v>33.00371666666667</v>
       </c>
       <c r="D34" t="n">
-        <v>36.55</v>
+        <v>46.8</v>
       </c>
       <c r="E34" t="n">
-        <v>-9.799999999999997</v>
+        <v>-13.79628333333333</v>
       </c>
       <c r="F34" t="n">
-        <v>25.92939460092482</v>
+        <v>30.51433266428049</v>
       </c>
       <c r="G34" t="n">
-        <v>38.59680733466195</v>
+        <v>45.48619791337757</v>
       </c>
       <c r="H34" t="n">
-        <v>-12.66741273373713</v>
+        <v>-14.97186524909708</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PAIR_030</t>
+          <t>PAIR_037</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2898,28 +2712,28 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>24.85</v>
+        <v>29.65</v>
       </c>
       <c r="D35" t="n">
-        <v>25.63333333333333</v>
+        <v>33.41666666666666</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7833333333333279</v>
+        <v>-3.766666666666659</v>
       </c>
       <c r="F35" t="n">
-        <v>25.11723460299349</v>
+        <v>28.67599222426386</v>
       </c>
       <c r="G35" t="n">
-        <v>26.87122394746974</v>
+        <v>34.42847320024024</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.753989344476249</v>
+        <v>-5.752480975976379</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PAIR_030</t>
+          <t>PAIR_037</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2928,232 +2742,22 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>148.25</v>
+        <v>163.7666666666667</v>
       </c>
       <c r="D36" t="n">
-        <v>132.1321833333333</v>
+        <v>136.9743</v>
       </c>
       <c r="E36" t="n">
-        <v>16.1178166666667</v>
+        <v>26.79236666666671</v>
       </c>
       <c r="F36" t="n">
-        <v>178.8509938017981</v>
+        <v>188.5603191017646</v>
       </c>
       <c r="G36" t="n">
-        <v>165.4445500478019</v>
+        <v>169.6534187990338</v>
       </c>
       <c r="H36" t="n">
-        <v>13.4064437539962</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>PAIR_032</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>CHARGING / REFUELING</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>21.51666666666667</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
-        <v>21.51666666666667</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.814768997799896</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.814768997799896</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>PAIR_032</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>STOP</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>3.666666666666667</v>
-      </c>
-      <c r="D38" t="n">
-        <v>16.43333333333333</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-12.76666666666666</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.1409484311311202</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.08388219724002884</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.05706623389109138</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>PAIR_032</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>IDLE</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>3.033333333333333</v>
-      </c>
-      <c r="D39" t="n">
-        <v>6.316666666666666</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-3.283333333333333</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.005421542589709919</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.02429801927644335</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-0.01887647668673343</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>PAIR_032</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>INCH</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>7.283333333333333</v>
-      </c>
-      <c r="D40" t="n">
-        <v>5</v>
-      </c>
-      <c r="E40" t="n">
-        <v>2.283333333333333</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.9244772773315977</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.2309310830082773</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.6935461943233203</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>PAIR_032</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>30.68333333333333</v>
-      </c>
-      <c r="D41" t="n">
-        <v>43.75068333333333</v>
-      </c>
-      <c r="E41" t="n">
-        <v>-13.06735</v>
-      </c>
-      <c r="F41" t="n">
-        <v>28.50220385729329</v>
-      </c>
-      <c r="G41" t="n">
-        <v>43.296144650172</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-14.79394079287871</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>PAIR_032</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>DEC</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>27.88333333333333</v>
-      </c>
-      <c r="D42" t="n">
-        <v>31.78333333333333</v>
-      </c>
-      <c r="E42" t="n">
-        <v>-3.900000000000002</v>
-      </c>
-      <c r="F42" t="n">
-        <v>26.94936248085756</v>
-      </c>
-      <c r="G42" t="n">
-        <v>33.18950889523448</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-6.240146414376923</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>PAIR_032</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>CRUISE</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>157.8226333333333</v>
-      </c>
-      <c r="D43" t="n">
-        <v>131.3409666666667</v>
-      </c>
-      <c r="E43" t="n">
-        <v>26.4816666666666</v>
-      </c>
-      <c r="F43" t="n">
-        <v>183.105394001778</v>
-      </c>
-      <c r="G43" t="n">
-        <v>163.8982401628798</v>
-      </c>
-      <c r="H43" t="n">
-        <v>19.20715383889819</v>
+        <v>18.9069003027308</v>
       </c>
     </row>
   </sheetData>
@@ -3214,19 +2818,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.402777777777779</v>
+        <v>25.55666666666666</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>7.402777777777779</v>
+        <v>25.55666666666666</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6916666666666665</v>
+        <v>23.4</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2886245454439411</v>
+        <v>0.2431610676685508</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -3239,22 +2843,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.283333333333334</v>
+        <v>25.24</v>
       </c>
       <c r="C3" t="n">
-        <v>6.644444444444443</v>
+        <v>17.1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6388888888888905</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>7.216666666666669</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2548072536546596</v>
+        <v>0.6853481671475011</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06801914414625496</v>
+        <v>0.1357887989486447</v>
       </c>
     </row>
     <row r="4">
@@ -3264,22 +2868,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.433333333333333</v>
+        <v>10.88666666666667</v>
       </c>
       <c r="C4" t="n">
-        <v>1.063888888888889</v>
+        <v>4.433333333333333</v>
       </c>
       <c r="D4" t="n">
-        <v>1.369444444444444</v>
+        <v>6.453333333333333</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9833333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008445713425528726</v>
+        <v>0.06347167107729518</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004049669879407226</v>
+        <v>0.02041065372186096</v>
       </c>
     </row>
     <row r="5">
@@ -3289,22 +2893,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.243425</v>
+        <v>4.73</v>
       </c>
       <c r="C5" t="n">
-        <v>1.236111111111111</v>
+        <v>3.716666666666666</v>
       </c>
       <c r="D5" t="n">
-        <v>1.007313888888889</v>
+        <v>1.013333333333333</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2750000000000002</v>
+        <v>2.283333333333333</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2625607285197823</v>
+        <v>0.4561839694795967</v>
       </c>
       <c r="G5" t="n">
-        <v>0.09066716862587565</v>
+        <v>0.265203250457141</v>
       </c>
     </row>
     <row r="6">
@@ -3314,22 +2918,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.30376111111111</v>
+        <v>54.18212666666666</v>
       </c>
       <c r="C6" t="n">
-        <v>17.18246666666667</v>
+        <v>58.05514666666667</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.878705555555554</v>
+        <v>-3.873020000000004</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.352441666666666</v>
+        <v>-3.560866666666676</v>
       </c>
       <c r="F6" t="n">
-        <v>13.87505127724761</v>
+        <v>54.1411699112384</v>
       </c>
       <c r="G6" t="n">
-        <v>17.7569291647084</v>
+        <v>55.92293105825396</v>
       </c>
     </row>
     <row r="7">
@@ -3339,22 +2943,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12.06111111111111</v>
+        <v>42.92018333333333</v>
       </c>
       <c r="C7" t="n">
-        <v>12.31388888888889</v>
+        <v>41.85</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2527777777777773</v>
+        <v>1.070183333333334</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1249999999999973</v>
+        <v>2.549999999999997</v>
       </c>
       <c r="F7" t="n">
-        <v>11.94063334165551</v>
+        <v>42.89250487829265</v>
       </c>
       <c r="G7" t="n">
-        <v>12.96374553627955</v>
+        <v>41.00591932781385</v>
       </c>
     </row>
     <row r="8">
@@ -3364,22 +2968,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>65.49639722222223</v>
+        <v>167.5333333333333</v>
       </c>
       <c r="C8" t="n">
-        <v>61.22428888888889</v>
+        <v>176.0881</v>
       </c>
       <c r="D8" t="n">
-        <v>4.272108333333326</v>
+        <v>-8.554766666666699</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.158900000000005</v>
+        <v>-17.66666666666669</v>
       </c>
       <c r="F8" t="n">
-        <v>79.85557209645967</v>
+        <v>202.4228729862558</v>
       </c>
       <c r="G8" t="n">
-        <v>75.69762267129458</v>
+        <v>206.0860679185309</v>
       </c>
     </row>
   </sheetData>
@@ -3450,28 +3054,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>14.43606594609487</v>
+        <v>17.90251378996816</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>8.25</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>27.5</v>
+        <v>32</v>
       </c>
       <c r="H2" t="n">
-        <v>29.5</v>
+        <v>33</v>
       </c>
       <c r="I2" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -3481,28 +3085,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>111.2241388888889</v>
+        <v>331.0489766666666</v>
       </c>
       <c r="D3" t="n">
-        <v>105.0984641350406</v>
+        <v>39.27441088267694</v>
       </c>
       <c r="E3" t="n">
-        <v>20.26271666666667</v>
+        <v>261.38705</v>
       </c>
       <c r="F3" t="n">
-        <v>28.9471125</v>
+        <v>343.8404</v>
       </c>
       <c r="G3" t="n">
-        <v>69.07236666666667</v>
+        <v>343.8404</v>
       </c>
       <c r="H3" t="n">
-        <v>198.3751333333334</v>
+        <v>350.0545666666667</v>
       </c>
       <c r="I3" t="n">
-        <v>251.8893</v>
+        <v>356.1224666666666</v>
       </c>
     </row>
     <row r="4">
@@ -3512,28 +3116,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>99.66508888888887</v>
+        <v>301.2432466666667</v>
       </c>
       <c r="D4" t="n">
-        <v>99.89170684399106</v>
+        <v>33.81861262232388</v>
       </c>
       <c r="E4" t="n">
-        <v>19.8356</v>
+        <v>244.9409666666667</v>
       </c>
       <c r="F4" t="n">
-        <v>21.19318333333333</v>
+        <v>299.0182166666667</v>
       </c>
       <c r="G4" t="n">
-        <v>54.64394166666666</v>
+        <v>311.5075166666667</v>
       </c>
       <c r="H4" t="n">
-        <v>181.8103375</v>
+        <v>317.3162</v>
       </c>
       <c r="I4" t="n">
-        <v>234.6249833333333</v>
+        <v>333.4333333333333</v>
       </c>
     </row>
     <row r="5">
@@ -3543,28 +3147,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>106.4856949564067</v>
+        <v>300.9047126511598</v>
       </c>
       <c r="D5" t="n">
-        <v>105.1797733217425</v>
+        <v>30.26991939981764</v>
       </c>
       <c r="E5" t="n">
-        <v>14.82892455320712</v>
+        <v>249.1268483717951</v>
       </c>
       <c r="F5" t="n">
-        <v>23.66821793817603</v>
+        <v>305.1072776594863</v>
       </c>
       <c r="G5" t="n">
-        <v>64.86053599951995</v>
+        <v>305.1665869122799</v>
       </c>
       <c r="H5" t="n">
-        <v>199.2032475096429</v>
+        <v>320.295003456412</v>
       </c>
       <c r="I5" t="n">
-        <v>240.4425765887812</v>
+        <v>324.8278468558257</v>
       </c>
     </row>
     <row r="6">
@@ -3574,28 +3178,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>106.5810333549341</v>
+        <v>303.4363210077263</v>
       </c>
       <c r="D6" t="n">
-        <v>105.1647356762908</v>
+        <v>31.48371626565701</v>
       </c>
       <c r="E6" t="n">
-        <v>15.14287648205564</v>
+        <v>249.9072012121763</v>
       </c>
       <c r="F6" t="n">
-        <v>23.66369347160319</v>
+        <v>305.2160753980956</v>
       </c>
       <c r="G6" t="n">
-        <v>64.91714314488451</v>
+        <v>310.4742418277487</v>
       </c>
       <c r="H6" t="n">
-        <v>199.1344023633156</v>
+        <v>320.9302329433269</v>
       </c>
       <c r="I6" t="n">
-        <v>240.7230050078111</v>
+        <v>330.6538536572841</v>
       </c>
     </row>
     <row r="7">
@@ -3605,28 +3209,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>68.18988860562877</v>
+        <v>66.77371167056229</v>
       </c>
       <c r="D7" t="n">
-        <v>6.471484361801513</v>
+        <v>2.293980454419871</v>
       </c>
       <c r="E7" t="n">
-        <v>57.87321624947242</v>
+        <v>63.84368844822295</v>
       </c>
       <c r="F7" t="n">
-        <v>65.08030092152619</v>
+        <v>65.68858194612334</v>
       </c>
       <c r="G7" t="n">
-        <v>69.38624567302695</v>
+        <v>66.1266599366777</v>
       </c>
       <c r="H7" t="n">
-        <v>71.92284660121217</v>
+        <v>69.09808681934425</v>
       </c>
       <c r="I7" t="n">
-        <v>76.08025778994646</v>
+        <v>69.11154120244322</v>
       </c>
     </row>
     <row r="8">
@@ -3636,28 +3240,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>67.04869791305295</v>
+        <v>65.2219937182538</v>
       </c>
       <c r="D8" t="n">
-        <v>14.94871508197339</v>
+        <v>1.963208456084527</v>
       </c>
       <c r="E8" t="n">
-        <v>38.26683233039817</v>
+        <v>62.88775311063549</v>
       </c>
       <c r="F8" t="n">
-        <v>67.97408377837463</v>
+        <v>63.46076786637193</v>
       </c>
       <c r="G8" t="n">
-        <v>69.49308018968046</v>
+        <v>65.88396841768795</v>
       </c>
       <c r="H8" t="n">
-        <v>75.17674629594654</v>
+        <v>66.42225595059593</v>
       </c>
       <c r="I8" t="n">
-        <v>80.50014146258407</v>
+        <v>67.45522324597772</v>
       </c>
     </row>
     <row r="9">
@@ -3667,28 +3271,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>11.55905000000001</v>
+        <v>29.80572999999998</v>
       </c>
       <c r="D9" t="n">
-        <v>7.257508664143034</v>
+        <v>10.83520696243526</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4271166666666701</v>
+        <v>16.44608333333329</v>
       </c>
       <c r="F9" t="n">
-        <v>6.851758333333341</v>
+        <v>22.6891333333333</v>
       </c>
       <c r="G9" t="n">
-        <v>14.428425</v>
+        <v>32.33288333333331</v>
       </c>
       <c r="H9" t="n">
-        <v>17.00642916666669</v>
+        <v>32.73836666666671</v>
       </c>
       <c r="I9" t="n">
-        <v>17.87836666666669</v>
+        <v>44.82218333333327</v>
       </c>
     </row>
     <row r="10">
@@ -3698,28 +3302,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.09533839852738731</v>
+        <v>-2.531608356566522</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1707668547452987</v>
+        <v>2.788039436665838</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3139519288485193</v>
+        <v>-5.826006801458391</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2385962243593225</v>
+        <v>-5.307654915468788</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.05660714536454314</v>
+        <v>-0.7803528403811981</v>
       </c>
       <c r="H10" t="n">
-        <v>0.03277071406436605</v>
+        <v>-0.6352294869149091</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09183174523019488</v>
+        <v>-0.1087977386093257</v>
       </c>
     </row>
     <row r="11">
@@ -3729,28 +3333,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>1.141190692575815</v>
+        <v>1.551717952308486</v>
       </c>
       <c r="D11" t="n">
-        <v>9.824156740237964</v>
+        <v>3.464061635230449</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.327473966294988</v>
+        <v>-3.611534797754771</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.735597575964086</v>
+        <v>0.2426915189897443</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.89396277864185</v>
+        <v>2.675830868748321</v>
       </c>
       <c r="H11" t="n">
-        <v>2.305736006612655</v>
+        <v>2.800828835487849</v>
       </c>
       <c r="I11" t="n">
-        <v>19.60638391907425</v>
+        <v>5.650773336071289</v>
       </c>
     </row>
     <row r="12">
@@ -3760,28 +3364,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>2.008333333333335</v>
+        <v>14.59333333333333</v>
       </c>
       <c r="D12" t="n">
-        <v>15.55316598709801</v>
+        <v>18.51363461524145</v>
       </c>
       <c r="E12" t="n">
         <v>-16.05</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.350000000000001</v>
+        <v>12.45</v>
       </c>
       <c r="G12" t="n">
-        <v>1.341666666666667</v>
+        <v>19.45</v>
       </c>
       <c r="H12" t="n">
-        <v>9.683333333333335</v>
+        <v>25.93333333333333</v>
       </c>
       <c r="I12" t="n">
-        <v>25.86666666666667</v>
+        <v>31.18333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -3791,28 +3395,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>7.402777777777779</v>
+        <v>25.55666666666667</v>
       </c>
       <c r="D13" t="n">
-        <v>10.94569127133629</v>
+        <v>4.174452725274962</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>20.98333333333333</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6916666666666665</v>
+        <v>23.4</v>
       </c>
       <c r="H13" t="n">
-        <v>16.48333333333333</v>
+        <v>30</v>
       </c>
       <c r="I13" t="n">
-        <v>21.51666666666667</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
@@ -3822,7 +3426,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -3853,28 +3457,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>7.402777777777779</v>
+        <v>25.55666666666667</v>
       </c>
       <c r="D15" t="n">
-        <v>10.94569127133629</v>
+        <v>4.174452725274962</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>20.98333333333333</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6916666666666665</v>
+        <v>23.4</v>
       </c>
       <c r="H15" t="n">
-        <v>16.48333333333333</v>
+        <v>30</v>
       </c>
       <c r="I15" t="n">
-        <v>21.51666666666667</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -3884,28 +3488,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2886245454439411</v>
+        <v>0.2431610676685508</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4094677048250032</v>
+        <v>0.09248541429851843</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.1419108710453242</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.1419108710453242</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05110463853192745</v>
+        <v>0.3053571304336727</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6366290676158857</v>
+        <v>0.3133132329092165</v>
       </c>
       <c r="I16" t="n">
-        <v>0.814768997799896</v>
+        <v>0.3133132329092165</v>
       </c>
     </row>
     <row r="17">
@@ -3915,7 +3519,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -3946,28 +3550,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2886245454439411</v>
+        <v>0.2431610676685508</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4094677048250032</v>
+        <v>0.09248541429851843</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.1419108710453242</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.1419108710453242</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05110463853192745</v>
+        <v>0.3053571304336727</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6366290676158857</v>
+        <v>0.3133132329092165</v>
       </c>
       <c r="I18" t="n">
-        <v>0.814768997799896</v>
+        <v>0.3133132329092165</v>
       </c>
     </row>
     <row r="19">
@@ -3977,28 +3581,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>7.283333333333334</v>
+        <v>25.24</v>
       </c>
       <c r="D19" t="n">
-        <v>9.878680748629007</v>
+        <v>13.93582314277369</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9166666666666667</v>
+        <v>23.65</v>
       </c>
       <c r="G19" t="n">
-        <v>3.666666666666667</v>
+        <v>23.65</v>
       </c>
       <c r="H19" t="n">
-        <v>8.791666666666666</v>
+        <v>37.61666666666667</v>
       </c>
       <c r="I19" t="n">
-        <v>25.86666666666667</v>
+        <v>37.61666666666667</v>
       </c>
     </row>
     <row r="20">
@@ -4008,25 +3612,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>6.644444444444443</v>
+        <v>17.1</v>
       </c>
       <c r="D20" t="n">
-        <v>8.499612191588943</v>
+        <v>0.9128709291752795</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>16.43333333333333</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>16.43333333333333</v>
       </c>
       <c r="G20" t="n">
-        <v>2.666666666666667</v>
+        <v>16.43333333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>13.65833333333333</v>
+        <v>18.1</v>
       </c>
       <c r="I20" t="n">
         <v>18.1</v>
@@ -4039,28 +3643,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6388888888888905</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>14.59204374790388</v>
+        <v>13.64007372088256</v>
       </c>
       <c r="E21" t="n">
-        <v>-14.43333333333333</v>
+        <v>-12.76666666666666</v>
       </c>
       <c r="F21" t="n">
-        <v>-9.574999999999996</v>
+        <v>5.549999999999997</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>7.216666666666669</v>
       </c>
       <c r="H21" t="n">
-        <v>3.875</v>
+        <v>19.51666666666667</v>
       </c>
       <c r="I21" t="n">
-        <v>25.86666666666667</v>
+        <v>21.18333333333334</v>
       </c>
     </row>
     <row r="22">
@@ -4070,28 +3674,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2548072536546596</v>
+        <v>0.6853481671475011</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4772770257242118</v>
+        <v>0.837076712352107</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>0.04165231879405064</v>
       </c>
       <c r="F22" t="n">
-        <v>0.00677143558736501</v>
+        <v>0.04165231879405064</v>
       </c>
       <c r="G22" t="n">
-        <v>0.08401708674029013</v>
+        <v>0.1409484311311202</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1409484311311202</v>
+        <v>1.601243883509142</v>
       </c>
       <c r="I22" t="n">
-        <v>1.219860917316257</v>
+        <v>1.601243883509142</v>
       </c>
     </row>
     <row r="23">
@@ -4101,25 +3705,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>0.06801914414625496</v>
+        <v>0.1357887989486447</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08619881717657346</v>
+        <v>0.07107604159811272</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.08388219724002884</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.08388219724002884</v>
       </c>
       <c r="G23" t="n">
-        <v>0.04194109862001442</v>
+        <v>0.08388219724002884</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1039085239044566</v>
+        <v>0.2136487015115684</v>
       </c>
       <c r="I23" t="n">
         <v>0.2136487015115684</v>
@@ -4132,28 +3736,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1867881095084046</v>
+        <v>0.5495593681988564</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5087702247991811</v>
+        <v>0.8295107072149039</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.08349822377647247</v>
+        <v>-0.1719963827175178</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.05452520278533614</v>
+        <v>-0.0422298784459782</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.05706623389109138</v>
       </c>
       <c r="H24" t="n">
-        <v>0.04279967541831853</v>
+        <v>1.387595181997574</v>
       </c>
       <c r="I24" t="n">
-        <v>1.219860917316257</v>
+        <v>1.517361686269113</v>
       </c>
     </row>
     <row r="25">
@@ -4163,28 +3767,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C25" t="n">
-        <v>2.433333333333333</v>
+        <v>10.88666666666667</v>
       </c>
       <c r="D25" t="n">
-        <v>2.527119572424964</v>
+        <v>13.57924478345128</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5083333333333333</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>2.358333333333333</v>
+        <v>3.033333333333333</v>
       </c>
       <c r="H25" t="n">
-        <v>2.945833333333333</v>
+        <v>25.7</v>
       </c>
       <c r="I25" t="n">
-        <v>6.85</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="26">
@@ -4194,28 +3798,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>1.063888888888889</v>
+        <v>4.433333333333333</v>
       </c>
       <c r="D26" t="n">
-        <v>2.573463223549729</v>
+        <v>4.082738051847069</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>6.316666666666666</v>
       </c>
       <c r="H26" t="n">
-        <v>0.05</v>
+        <v>6.983333333333333</v>
       </c>
       <c r="I26" t="n">
-        <v>6.316666666666666</v>
+        <v>8.733333333333333</v>
       </c>
     </row>
     <row r="27">
@@ -4225,28 +3829,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>1.369444444444444</v>
+        <v>6.453333333333331</v>
       </c>
       <c r="D27" t="n">
-        <v>3.391712393904141</v>
+        <v>14.88463693432482</v>
       </c>
       <c r="E27" t="n">
+        <v>-8.733333333333333</v>
+      </c>
+      <c r="F27" t="n">
         <v>-3.283333333333333</v>
       </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
       <c r="G27" t="n">
-        <v>0.9833333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="H27" t="n">
-        <v>2.504166666666666</v>
+        <v>18.71666666666667</v>
       </c>
       <c r="I27" t="n">
-        <v>6.85</v>
+        <v>25.63333333333333</v>
       </c>
     </row>
     <row r="28">
@@ -4256,13 +3860,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>0.008445713425528726</v>
+        <v>0.06347167107729518</v>
       </c>
       <c r="D28" t="n">
-        <v>0.01348150709902683</v>
+        <v>0.08446658446722083</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -4271,13 +3875,13 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.002710771294854959</v>
+        <v>0.005421542589709919</v>
       </c>
       <c r="H28" t="n">
-        <v>0.009396738419882941</v>
+        <v>0.155968406398383</v>
       </c>
       <c r="I28" t="n">
-        <v>0.03453093426685515</v>
+        <v>0.155968406398383</v>
       </c>
     </row>
     <row r="29">
@@ -4287,13 +3891,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>0.004049669879407226</v>
+        <v>0.02041065372186096</v>
       </c>
       <c r="D29" t="n">
-        <v>0.009919624831265987</v>
+        <v>0.02035415981013516</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -4302,13 +3906,13 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.02429801927644335</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.03091495950618035</v>
       </c>
       <c r="I29" t="n">
-        <v>0.02429801927644335</v>
+        <v>0.0468402898266811</v>
       </c>
     </row>
     <row r="30">
@@ -4318,28 +3922,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>0.004396043546121499</v>
+        <v>0.04306101735543423</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01759382093121824</v>
+        <v>0.09116411906391592</v>
       </c>
       <c r="E30" t="n">
+        <v>-0.0468402898266811</v>
+      </c>
+      <c r="F30" t="n">
         <v>-0.01887647668673343</v>
       </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.008041352772455461</v>
+        <v>0.1250534468922027</v>
       </c>
       <c r="I30" t="n">
-        <v>0.03453093426685515</v>
+        <v>0.155968406398383</v>
       </c>
     </row>
     <row r="31">
@@ -4349,28 +3953,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>2.243425</v>
+        <v>4.73</v>
       </c>
       <c r="D31" t="n">
-        <v>3.072119869871797</v>
+        <v>3.787578382027228</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7333333333333335</v>
+        <v>7.283333333333333</v>
       </c>
       <c r="H31" t="n">
-        <v>3.899579166666666</v>
+        <v>7.6</v>
       </c>
       <c r="I31" t="n">
-        <v>7.283333333333333</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="32">
@@ -4380,28 +3984,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>1.236111111111111</v>
+        <v>3.716666666666666</v>
       </c>
       <c r="D32" t="n">
-        <v>1.933201623866098</v>
+        <v>1.795635139875458</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="F32" t="n">
-        <v>0.02083333333333333</v>
+        <v>1.75</v>
       </c>
       <c r="G32" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="H32" t="n">
-        <v>1.291666666666667</v>
+        <v>5</v>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>5.083333333333333</v>
       </c>
     </row>
     <row r="33">
@@ -4411,28 +4015,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>1.007313888888889</v>
+        <v>1.013333333333333</v>
       </c>
       <c r="D33" t="n">
-        <v>1.434199103658618</v>
+        <v>3.958314035040676</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.08333333333333333</v>
+        <v>-4.5</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>-1.166666666666667</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2750000000000002</v>
+        <v>2.283333333333333</v>
       </c>
       <c r="H33" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="I33" t="n">
-        <v>3.293883333333333</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="34">
@@ -4442,25 +4046,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2625607285197823</v>
+        <v>0.4561839694795967</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3932788629732992</v>
+        <v>0.2840189100570285</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>0.2289474824354939</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>0.2289474824354939</v>
       </c>
       <c r="G34" t="n">
-        <v>0.04000008804585436</v>
+        <v>0.4492738025976991</v>
       </c>
       <c r="H34" t="n">
-        <v>0.4481652322944679</v>
+        <v>0.4492738025976991</v>
       </c>
       <c r="I34" t="n">
         <v>0.9244772773315977</v>
@@ -4473,28 +4077,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C35" t="n">
-        <v>0.09066716862587565</v>
+        <v>0.265203250457141</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1066099975743054</v>
+        <v>0.03918320424270517</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>0.2309310830082773</v>
       </c>
       <c r="F35" t="n">
-        <v>0.001368794275984173</v>
+        <v>0.2309310830082773</v>
       </c>
       <c r="G35" t="n">
-        <v>0.05345317653979344</v>
+        <v>0.2495284473497653</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1799819757444548</v>
+        <v>0.3073128194596925</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2309310830082773</v>
+        <v>0.3073128194596925</v>
       </c>
     </row>
     <row r="36">
@@ -4504,25 +4108,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1718935598939067</v>
+        <v>0.1909807190224558</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2957136691847062</v>
+        <v>0.3053806291186553</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.02143099988394148</v>
+        <v>-0.07836533702419862</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.00410638282795252</v>
+        <v>-0.02058096491427139</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.1419609831380066</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2735410065209984</v>
+        <v>0.2183427195894218</v>
       </c>
       <c r="I36" t="n">
         <v>0.6935461943233203</v>
@@ -4535,28 +4139,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>14.30376111111111</v>
+        <v>54.18212666666666</v>
       </c>
       <c r="D37" t="n">
-        <v>12.09509932843173</v>
+        <v>12.01350051948848</v>
       </c>
       <c r="E37" t="n">
-        <v>2.616666666666667</v>
+        <v>33.00371666666667</v>
       </c>
       <c r="F37" t="n">
-        <v>4.421091666666667</v>
+        <v>56.67031666666666</v>
       </c>
       <c r="G37" t="n">
-        <v>11.06666666666667</v>
+        <v>58.38913333333333</v>
       </c>
       <c r="H37" t="n">
-        <v>23.90416666666667</v>
+        <v>61.42373333333333</v>
       </c>
       <c r="I37" t="n">
-        <v>30.68333333333333</v>
+        <v>61.42373333333333</v>
       </c>
     </row>
     <row r="38">
@@ -4566,28 +4170,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C38" t="n">
-        <v>17.18246666666667</v>
+        <v>58.05514666666667</v>
       </c>
       <c r="D38" t="n">
-        <v>18.10328983617496</v>
+        <v>6.690098608634258</v>
       </c>
       <c r="E38" t="n">
-        <v>3.466666666666667</v>
+        <v>46.8</v>
       </c>
       <c r="F38" t="n">
-        <v>4.253920833333334</v>
+        <v>57.69085</v>
       </c>
       <c r="G38" t="n">
-        <v>7.650000000000002</v>
+        <v>60.01821666666667</v>
       </c>
       <c r="H38" t="n">
-        <v>30.00416666666667</v>
+        <v>61.95</v>
       </c>
       <c r="I38" t="n">
-        <v>43.75068333333333</v>
+        <v>63.81666666666667</v>
       </c>
     </row>
     <row r="39">
@@ -4597,28 +4201,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C39" t="n">
-        <v>-2.878705555555554</v>
+        <v>-3.873020000000004</v>
       </c>
       <c r="D39" t="n">
-        <v>7.164202208098157</v>
+        <v>6.982048392707623</v>
       </c>
       <c r="E39" t="n">
-        <v>-13.06735</v>
+        <v>-13.79628333333333</v>
       </c>
       <c r="F39" t="n">
-        <v>-7.702695833333332</v>
+        <v>-7.146350000000012</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.352441666666666</v>
+        <v>-3.560866666666676</v>
       </c>
       <c r="H39" t="n">
-        <v>2.151475</v>
+        <v>1.405516666666664</v>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>3.732883333333334</v>
       </c>
     </row>
     <row r="40">
@@ -4628,28 +4232,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C40" t="n">
-        <v>13.8750512772476</v>
+        <v>54.14116991123841</v>
       </c>
       <c r="D40" t="n">
-        <v>11.3921317067655</v>
+        <v>13.21710444577263</v>
       </c>
       <c r="E40" t="n">
-        <v>2.15122666286036</v>
+        <v>30.51433266428049</v>
       </c>
       <c r="F40" t="n">
-        <v>4.67688607754814</v>
+        <v>59.19131521643719</v>
       </c>
       <c r="G40" t="n">
-        <v>11.35048097465013</v>
+        <v>60.30149638549678</v>
       </c>
       <c r="H40" t="n">
-        <v>23.42029080530071</v>
+        <v>60.30869650602873</v>
       </c>
       <c r="I40" t="n">
-        <v>28.50220385729329</v>
+        <v>60.39000878394881</v>
       </c>
     </row>
     <row r="41">
@@ -4659,28 +4263,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41" t="n">
-        <v>17.7569291647084</v>
+        <v>55.92293105825395</v>
       </c>
       <c r="D41" t="n">
-        <v>18.30548587328532</v>
+        <v>6.208755132550696</v>
       </c>
       <c r="E41" t="n">
-        <v>3.237008300255083</v>
+        <v>45.48619791337757</v>
       </c>
       <c r="F41" t="n">
-        <v>4.483962481655899</v>
+        <v>55.580881691352</v>
       </c>
       <c r="G41" t="n">
-        <v>8.50454243297977</v>
+        <v>57.92889382509147</v>
       </c>
       <c r="H41" t="n">
-        <v>32.01781161373179</v>
+        <v>59.1588856042147</v>
       </c>
       <c r="I41" t="n">
-        <v>43.296144650172</v>
+        <v>61.45979625723403</v>
       </c>
     </row>
     <row r="42">
@@ -4690,28 +4294,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C42" t="n">
-        <v>-3.881877887460791</v>
+        <v>-1.781761147015555</v>
       </c>
       <c r="D42" t="n">
-        <v>7.867696097869051</v>
+        <v>7.79305029272399</v>
       </c>
       <c r="E42" t="n">
-        <v>-14.79394079287871</v>
+        <v>-14.97186524909708</v>
       </c>
       <c r="F42" t="n">
-        <v>-9.772004959651531</v>
+        <v>-2.268481040796843</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.9237607296530252</v>
+        <v>1.231123179734105</v>
       </c>
       <c r="H42" t="n">
-        <v>1.613654564774736</v>
+        <v>2.372602560405312</v>
       </c>
       <c r="I42" t="n">
-        <v>3.61215496748706</v>
+        <v>4.727814814676734</v>
       </c>
     </row>
     <row r="43">
@@ -4721,28 +4325,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C43" t="n">
-        <v>12.06111111111111</v>
+        <v>42.92018333333333</v>
       </c>
       <c r="D43" t="n">
-        <v>11.34268078574935</v>
+        <v>7.500862961556861</v>
       </c>
       <c r="E43" t="n">
-        <v>2.816666666666667</v>
+        <v>29.65</v>
       </c>
       <c r="F43" t="n">
-        <v>3.670833333333333</v>
+        <v>45.18333333333333</v>
       </c>
       <c r="G43" t="n">
-        <v>6.658333333333333</v>
+        <v>45.18333333333333</v>
       </c>
       <c r="H43" t="n">
-        <v>20.92083333333333</v>
+        <v>46.80091666666667</v>
       </c>
       <c r="I43" t="n">
-        <v>27.88333333333333</v>
+        <v>47.78333333333333</v>
       </c>
     </row>
     <row r="44">
@@ -4752,28 +4356,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C44" t="n">
-        <v>12.31388888888889</v>
+        <v>41.85</v>
       </c>
       <c r="D44" t="n">
-        <v>12.90302039001664</v>
+        <v>5.165497179469868</v>
       </c>
       <c r="E44" t="n">
-        <v>2.966666666666667</v>
+        <v>33.41666666666666</v>
       </c>
       <c r="F44" t="n">
-        <v>3.320833333333333</v>
+        <v>41.38333333333333</v>
       </c>
       <c r="G44" t="n">
-        <v>5.233333333333333</v>
+        <v>42.63333333333333</v>
       </c>
       <c r="H44" t="n">
-        <v>20.79583333333333</v>
+        <v>44.95</v>
       </c>
       <c r="I44" t="n">
-        <v>31.78333333333333</v>
+        <v>46.86666666666667</v>
       </c>
     </row>
     <row r="45">
@@ -4783,28 +4387,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.2527777777777773</v>
+        <v>1.070183333333334</v>
       </c>
       <c r="D45" t="n">
-        <v>2.325401199952546</v>
+        <v>3.059244873466866</v>
       </c>
       <c r="E45" t="n">
-        <v>-3.900000000000002</v>
+        <v>-3.766666666666659</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.220833333333332</v>
+        <v>-0.0657499999999942</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.1249999999999973</v>
+        <v>2.549999999999997</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9958333333333336</v>
+        <v>2.833333333333329</v>
       </c>
       <c r="I45" t="n">
-        <v>2.85</v>
+        <v>3.799999999999997</v>
       </c>
     </row>
     <row r="46">
@@ -4814,28 +4418,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C46" t="n">
-        <v>11.94063334165551</v>
+        <v>42.89250487829265</v>
       </c>
       <c r="D46" t="n">
-        <v>11.19253388987332</v>
+        <v>8.158325656477704</v>
       </c>
       <c r="E46" t="n">
-        <v>2.457618245090195</v>
+        <v>28.67599222426386</v>
       </c>
       <c r="F46" t="n">
-        <v>3.636635870838528</v>
+        <v>44.61908932592698</v>
       </c>
       <c r="G46" t="n">
-        <v>6.850412925856716</v>
+        <v>44.61908932592698</v>
       </c>
       <c r="H46" t="n">
-        <v>21.19056569629372</v>
+        <v>47.93000682714188</v>
       </c>
       <c r="I46" t="n">
-        <v>26.94936248085756</v>
+        <v>48.61834668820352</v>
       </c>
     </row>
     <row r="47">
@@ -4845,28 +4449,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C47" t="n">
-        <v>12.96374553627955</v>
+        <v>41.00591932781384</v>
       </c>
       <c r="D47" t="n">
-        <v>13.48523462817115</v>
+        <v>4.6880075317008</v>
       </c>
       <c r="E47" t="n">
-        <v>2.895199368072901</v>
+        <v>34.42847320024024</v>
       </c>
       <c r="F47" t="n">
-        <v>3.312126877052598</v>
+        <v>38.88632527176938</v>
       </c>
       <c r="G47" t="n">
-        <v>5.866110585152168</v>
+        <v>41.61929530648353</v>
       </c>
       <c r="H47" t="n">
-        <v>22.09508625357266</v>
+        <v>43.16292539518683</v>
       </c>
       <c r="I47" t="n">
-        <v>33.18950889523448</v>
+        <v>46.93257746538925</v>
       </c>
     </row>
     <row r="48">
@@ -4876,28 +4480,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C48" t="n">
-        <v>-1.023112194624041</v>
+        <v>1.886585550478798</v>
       </c>
       <c r="D48" t="n">
-        <v>2.787109446309921</v>
+        <v>5.006535599895053</v>
       </c>
       <c r="E48" t="n">
-        <v>-6.240146414376923</v>
+        <v>-5.752480975976379</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.424887289102863</v>
+        <v>0.99742936175263</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.05657104515008471</v>
+        <v>1.456163930740146</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3246489159927178</v>
+        <v>5.732764054157599</v>
       </c>
       <c r="I48" t="n">
-        <v>1.643885804312985</v>
+        <v>6.999051381719994</v>
       </c>
     </row>
     <row r="49">
@@ -4907,28 +4511,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C49" t="n">
-        <v>65.49639722222221</v>
+        <v>167.5333333333333</v>
       </c>
       <c r="D49" t="n">
-        <v>70.00668132156737</v>
+        <v>18.35176346355364</v>
       </c>
       <c r="E49" t="n">
-        <v>8.675850000000001</v>
+        <v>150.2833333333333</v>
       </c>
       <c r="F49" t="n">
-        <v>11.6631875</v>
+        <v>150.2833333333333</v>
       </c>
       <c r="G49" t="n">
-        <v>33.29618333333333</v>
+        <v>163.7666666666667</v>
       </c>
       <c r="H49" t="n">
-        <v>124.9005541666667</v>
+        <v>184.9833333333333</v>
       </c>
       <c r="I49" t="n">
-        <v>157.8226333333333</v>
+        <v>188.35</v>
       </c>
     </row>
     <row r="50">
@@ -4938,28 +4542,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C50" t="n">
-        <v>61.22428888888889</v>
+        <v>176.0881</v>
       </c>
       <c r="D50" t="n">
-        <v>57.82147746437369</v>
+        <v>26.44851647484223</v>
       </c>
       <c r="E50" t="n">
-        <v>11.85226666666667</v>
+        <v>136.9743</v>
       </c>
       <c r="F50" t="n">
-        <v>14.2654875</v>
+        <v>167.95</v>
       </c>
       <c r="G50" t="n">
-        <v>39.08855</v>
+        <v>176.3828666666667</v>
       </c>
       <c r="H50" t="n">
-        <v>114.166925</v>
+        <v>192.5166666666667</v>
       </c>
       <c r="I50" t="n">
-        <v>132.1321833333333</v>
+        <v>206.6166666666667</v>
       </c>
     </row>
     <row r="51">
@@ -4969,28 +4573,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C51" t="n">
-        <v>4.272108333333326</v>
+        <v>-8.554766666666699</v>
       </c>
       <c r="D51" t="n">
-        <v>13.88646892912404</v>
+        <v>26.71757587032679</v>
       </c>
       <c r="E51" t="n">
-        <v>-7.792583333333333</v>
+        <v>-42.23333333333341</v>
       </c>
       <c r="F51" t="n">
-        <v>-5.693758333333334</v>
+        <v>-18.26666666666671</v>
       </c>
       <c r="G51" t="n">
-        <v>-1.158900000000005</v>
+        <v>-17.66666666666669</v>
       </c>
       <c r="H51" t="n">
-        <v>12.06033333333336</v>
+        <v>8.600466666666591</v>
       </c>
       <c r="I51" t="n">
-        <v>26.4816666666666</v>
+        <v>26.79236666666671</v>
       </c>
     </row>
     <row r="52">
@@ -5000,28 +4604,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C52" t="n">
-        <v>79.85557209645967</v>
+        <v>202.4228729862558</v>
       </c>
       <c r="D52" t="n">
-        <v>82.17305455734203</v>
+        <v>10.24523118381264</v>
       </c>
       <c r="E52" t="n">
-        <v>9.000218727940311</v>
+        <v>188.5603191017646</v>
       </c>
       <c r="F52" t="n">
-        <v>15.27535858106732</v>
+        <v>199.2264841873632</v>
       </c>
       <c r="G52" t="n">
-        <v>46.5834727708108</v>
+        <v>199.2785933196247</v>
       </c>
       <c r="H52" t="n">
-        <v>153.4120335349016</v>
+        <v>211.201579175843</v>
       </c>
       <c r="I52" t="n">
-        <v>183.105394001778</v>
+        <v>213.8473891466835</v>
       </c>
     </row>
     <row r="53">
@@ -5031,28 +4635,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C53" t="n">
-        <v>75.69762267129458</v>
+        <v>206.0860679185309</v>
       </c>
       <c r="D53" t="n">
-        <v>73.86093023956795</v>
+        <v>22.35685648972044</v>
       </c>
       <c r="E53" t="n">
-        <v>9.010668813727651</v>
+        <v>169.6534187990338</v>
       </c>
       <c r="F53" t="n">
-        <v>15.70063244115852</v>
+        <v>203.7785279380628</v>
       </c>
       <c r="G53" t="n">
-        <v>50.60334784461</v>
+        <v>212.1576082862871</v>
       </c>
       <c r="H53" t="n">
-        <v>143.4939075889099</v>
+        <v>215.4860733436561</v>
       </c>
       <c r="I53" t="n">
-        <v>165.4445500478019</v>
+        <v>229.3547112256146</v>
       </c>
     </row>
     <row r="54">
@@ -5062,28 +4666,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C54" t="n">
-        <v>4.157949425165089</v>
+        <v>-3.663194932275081</v>
       </c>
       <c r="D54" t="n">
-        <v>9.798993626168922</v>
+        <v>14.27559485849499</v>
       </c>
       <c r="E54" t="n">
-        <v>-5.185757132787998</v>
+        <v>-16.20748002403141</v>
       </c>
       <c r="F54" t="n">
-        <v>-2.143107282554629</v>
+        <v>-15.50732207893111</v>
       </c>
       <c r="G54" t="n">
-        <v>0.1869245528472652</v>
+        <v>-4.552043750699596</v>
       </c>
       <c r="H54" t="n">
-        <v>10.15090761336762</v>
+        <v>-0.9560291104440921</v>
       </c>
       <c r="I54" t="n">
-        <v>19.20715383889819</v>
+        <v>18.9069003027308</v>
       </c>
     </row>
   </sheetData>
@@ -5139,19 +4743,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>111.2241388888889</v>
+        <v>331.0489766666666</v>
       </c>
       <c r="D2" t="n">
-        <v>99.66508888888887</v>
+        <v>301.2432466666667</v>
       </c>
       <c r="E2" t="n">
-        <v>11.55905000000001</v>
+        <v>29.80572999999998</v>
       </c>
       <c r="F2" t="n">
-        <v>14.428425</v>
+        <v>32.33288333333331</v>
       </c>
     </row>
   </sheetData>
